--- a/02_spreadsheet/spreadsheet_workbook.xlsx
+++ b/02_spreadsheet/spreadsheet_workbook.xlsx
@@ -4,21 +4,32 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="transactions_raw" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="PivotTables" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="cleaned_transactions" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="merchant_risk_summary" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="merchant_master" sheetId="5" r:id="rId8"/>
+    <sheet state="visible" name="gateway" sheetId="6" r:id="rId9"/>
+    <sheet state="visible" name="exchange_rates" sheetId="7" r:id="rId10"/>
+    <sheet state="visible" name="ledger" sheetId="8" r:id="rId11"/>
+    <sheet state="visible" name="users" sheetId="9" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">transactions_raw!$A$1:$AG$31</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">transactions_raw!$A$1:$AG$32</definedName>
   </definedNames>
   <calcPr/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId13"/>
+  </pivotCaches>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="3ngH2JSPQMnBKfXQCpvHVXq72t0rzeNc3RGo7Oikd+Y="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId14" roundtripDataChecksum="whnQJcmvotHogGuyCQfp3Shs4AtVzj3RkmJfU0xJVzE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="171">
   <si>
     <t>transaction_id</t>
   </si>
@@ -348,6 +359,189 @@
   </si>
   <si>
     <t>score:47</t>
+  </si>
+  <si>
+    <t>Top Region by GMV</t>
+  </si>
+  <si>
+    <t>Top Merchant by Captured GMV</t>
+  </si>
+  <si>
+    <t>SUM of raw_amount_USD</t>
+  </si>
+  <si>
+    <t>SUM of raw_amount</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>merchant_id</t>
+  </si>
+  <si>
+    <t>account_manager</t>
+  </si>
+  <si>
+    <t>merchant_category</t>
+  </si>
+  <si>
+    <t>default_region</t>
+  </si>
+  <si>
+    <t>M001</t>
+  </si>
+  <si>
+    <t>Aisha Khan</t>
+  </si>
+  <si>
+    <t>Grocery</t>
+  </si>
+  <si>
+    <t>M002</t>
+  </si>
+  <si>
+    <t>Rohan Mehta</t>
+  </si>
+  <si>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>M003</t>
+  </si>
+  <si>
+    <t>Elena Rossi</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>M004</t>
+  </si>
+  <si>
+    <t>Marcus Lee</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>M005</t>
+  </si>
+  <si>
+    <t>Nina Weber</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>amount_usd</t>
+  </si>
+  <si>
+    <t>R001</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>R002</t>
+  </si>
+  <si>
+    <t>R003</t>
+  </si>
+  <si>
+    <t>R005</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>R006</t>
+  </si>
+  <si>
+    <t>R007</t>
+  </si>
+  <si>
+    <t>R008</t>
+  </si>
+  <si>
+    <t>R009</t>
+  </si>
+  <si>
+    <t>R011</t>
+  </si>
+  <si>
+    <t>rate_date</t>
+  </si>
+  <si>
+    <t>usd_rate</t>
+  </si>
+  <si>
+    <t>R004</t>
+  </si>
+  <si>
+    <t>R010</t>
+  </si>
+  <si>
+    <t>user_name</t>
+  </si>
+  <si>
+    <t>signup_date</t>
+  </si>
+  <si>
+    <t>user_region</t>
+  </si>
+  <si>
+    <t>risk_tier</t>
+  </si>
+  <si>
+    <t>Aarav Shah</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>Meera Iyer</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>Kabir Jain</t>
+  </si>
+  <si>
+    <t>Sofia Rossi</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Vikram Nair</t>
+  </si>
+  <si>
+    <t>Riya Gupta</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>Noah Kim</t>
+  </si>
+  <si>
+    <t>Singapore</t>
+  </si>
+  <si>
+    <t>Ishaan Verma</t>
+  </si>
+  <si>
+    <t>Emma Brooks</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Liam Carter</t>
   </si>
 </sst>
 </file>
@@ -357,7 +551,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -372,6 +566,17 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -388,7 +593,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -401,6 +606,17 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -411,6 +627,1013 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" invalid="1" refreshOnLoad="1">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:S31" sheet="transactions_raw"/>
+  </cacheSource>
+  <cacheFields>
+    <cacheField name="transaction_id" numFmtId="0">
+      <sharedItems>
+        <s v="T001"/>
+        <s v="T002"/>
+        <s v="T003"/>
+        <s v="T004"/>
+        <s v="T005"/>
+        <s v="T006"/>
+        <s v="T007"/>
+        <s v="T008"/>
+        <s v="T009"/>
+        <s v="T010"/>
+        <s v="T011"/>
+        <s v="T012"/>
+        <s v="T013"/>
+        <s v="T014"/>
+        <s v="T015"/>
+        <s v="T016"/>
+        <s v="T017"/>
+        <s v="T018"/>
+        <s v="T019"/>
+        <s v="T020"/>
+        <s v="T021"/>
+        <s v="T022"/>
+        <s v="T023"/>
+        <s v="T024"/>
+        <s v="T025"/>
+        <s v="T026"/>
+        <s v="T027"/>
+        <s v="T028"/>
+        <s v="T029"/>
+        <s v="T030"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="transaction_date" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsDate="1" containsString="0">
+        <d v="2026-03-01T00:00:00Z"/>
+        <d v="2026-03-02T00:00:00Z"/>
+        <d v="2026-03-03T00:00:00Z"/>
+        <d v="2026-03-04T00:00:00Z"/>
+        <d v="2026-03-05T00:00:00Z"/>
+        <d v="2026-03-06T00:00:00Z"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="transaction_date_cleaned" numFmtId="0">
+      <sharedItems>
+        <s v="2026_03-01"/>
+        <s v="2026_03-02"/>
+        <s v="2026_03-03"/>
+        <s v="2026_03-04"/>
+        <s v="2026_03-05"/>
+        <s v="2026_03-06"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="merchant_name" numFmtId="0">
+      <sharedItems>
+        <s v="alpha mart"/>
+        <s v="BETA STORES"/>
+        <s v="Beta  Stores"/>
+        <s v="Alpha  Mart"/>
+        <s v="City Pharma"/>
+        <s v="Eco Home"/>
+        <s v="DELTA TRAVELS"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="merchant_name_cleaned" numFmtId="0">
+      <sharedItems>
+        <s v="Alpha Mart"/>
+        <s v="Beta Stores"/>
+        <s v="City Pharma"/>
+        <s v="Eco Home"/>
+        <s v="Delta Travels"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="raw_amount" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1">
+        <n v="420000.0"/>
+        <n v="210000.0"/>
+        <n v="510000.0"/>
+        <n v="160000.0"/>
+        <n v="390000.0"/>
+        <n v="275000.0"/>
+        <n v="450000.0"/>
+        <n v="340000.0"/>
+        <n v="125000.0"/>
+        <n v="610000.0"/>
+        <n v="195000.0"/>
+        <n v="250000.0"/>
+        <n v="310000.0"/>
+        <n v="470000.0"/>
+        <n v="130000.0"/>
+        <n v="220000.0"/>
+        <n v="180000.0"/>
+        <n v="145000.0"/>
+        <n v="260000.0"/>
+        <n v="520000.0"/>
+        <n v="330000.0"/>
+        <n v="410000.0"/>
+        <n v="5200.0"/>
+        <n v="6100.0"/>
+        <n v="2800.0"/>
+        <n v="3300.0"/>
+        <n v="7200.0"/>
+        <n v="3100.0"/>
+        <n v="2500.0"/>
+        <n v="1800.0"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="currency_value_in_USD" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1">
+        <n v="0.0119"/>
+        <n v="0.012"/>
+        <n v="0.0121"/>
+        <n v="0.0118"/>
+        <n v="1.08"/>
+        <n v="1.09"/>
+        <n v="1.0"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="raw_amount_USD" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1">
+        <n v="4998.0"/>
+        <n v="2499.0"/>
+        <n v="6069.0"/>
+        <n v="1920.0"/>
+        <n v="4680.0"/>
+        <n v="3300.0"/>
+        <n v="5400.0"/>
+        <n v="4114.0"/>
+        <n v="1512.5"/>
+        <n v="7381.0"/>
+        <n v="2359.5"/>
+        <n v="3000.0"/>
+        <n v="3720.0"/>
+        <n v="5640.0"/>
+        <n v="1560.0"/>
+        <n v="2596.0"/>
+        <n v="2124.0"/>
+        <n v="1711.0"/>
+        <n v="3068.0"/>
+        <n v="6136.0"/>
+        <n v="3927.0000000000005"/>
+        <n v="4879.0"/>
+        <n v="5616.0"/>
+        <n v="6649.000000000001"/>
+        <n v="3024.0"/>
+        <n v="3597.0000000000005"/>
+        <n v="7200.0"/>
+        <n v="3100.0"/>
+        <n v="2500.0"/>
+        <n v="1800.0"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="currency" numFmtId="0">
+      <sharedItems>
+        <s v="INR"/>
+        <s v="EUR"/>
+        <s v="USD"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="status" numFmtId="0">
+      <sharedItems>
+        <s v="captured"/>
+        <s v="failed e05 timeout"/>
+        <s v="chargeback"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="status_cleaned" numFmtId="0">
+      <sharedItems>
+        <s v="Captured"/>
+        <s v="Failed E05 Timeout"/>
+        <s v="Chargeback"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="risk_score">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1">
+        <s v="score:62"/>
+        <n v="55.0"/>
+        <n v="71.0"/>
+        <n v="68.0"/>
+        <n v="58.0"/>
+        <s v="score:64"/>
+        <s v="risk-83"/>
+        <n v="59.0"/>
+        <n v="46.0"/>
+        <s v="risk-77"/>
+        <m/>
+        <s v="risk-61"/>
+        <s v="score:54"/>
+        <s v="risk-73"/>
+        <s v="score:52"/>
+        <s v="risk-69"/>
+        <s v="score:72"/>
+        <s v="risk-86"/>
+        <s v="score:67"/>
+        <n v="75.0"/>
+        <s v="score:63"/>
+        <n v="60.0"/>
+        <n v="42.0"/>
+        <s v="score:65"/>
+        <n v="38.0"/>
+        <n v="44.0"/>
+        <n v="49.0"/>
+        <s v="risk-41"/>
+        <s v="score:58"/>
+        <s v="score:47"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="risk_score_cleaned">
+      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1">
+        <n v="62.0"/>
+        <n v="55.0"/>
+        <n v="71.0"/>
+        <n v="68.0"/>
+        <n v="58.0"/>
+        <n v="64.0"/>
+        <n v="83.0"/>
+        <n v="59.0"/>
+        <n v="46.0"/>
+        <n v="77.0"/>
+        <s v="INVALID_OR_MISSING"/>
+        <n v="61.0"/>
+        <n v="54.0"/>
+        <n v="73.0"/>
+        <n v="52.0"/>
+        <n v="69.0"/>
+        <n v="72.0"/>
+        <n v="86.0"/>
+        <n v="67.0"/>
+        <n v="75.0"/>
+        <n v="63.0"/>
+        <n v="60.0"/>
+        <n v="42.0"/>
+        <n v="65.0"/>
+        <n v="38.0"/>
+        <n v="44.0"/>
+        <n v="49.0"/>
+        <n v="41.0"/>
+        <n v="47.0"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="gateway_region" numFmtId="0">
+      <sharedItems containsBlank="1">
+        <s v="APAC"/>
+        <m/>
+        <s v="EU"/>
+        <s v="us"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="gateway_region_cleaned" numFmtId="0">
+      <sharedItems>
+        <s v="APAC"/>
+        <s v="EU"/>
+        <s v="US"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="user_id" numFmtId="0">
+      <sharedItems>
+        <s v="U001"/>
+        <s v="U002"/>
+        <s v="U003"/>
+        <s v="U004"/>
+        <s v="U005"/>
+        <s v="U006"/>
+        <s v="U007"/>
+        <s v="U008"/>
+        <s v="U009"/>
+        <s v="U010"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="payment_method" numFmtId="0">
+      <sharedItems>
+        <s v="UPI"/>
+        <s v="Card"/>
+        <s v="NetBanking"/>
+        <s v="Wallet"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="high_value_flag" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1">
+        <n v="0.0"/>
+        <n v="1.0"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="high_risk_flag" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1">
+        <n v="0.0"/>
+        <n v="1.0"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTables" cacheId="0" dataCaption="" compact="0" compactData="0">
+  <location ref="A2:C6" firstHeaderRow="0" firstDataRow="2" firstDataCol="0"/>
+  <pivotFields>
+    <pivotField name="transaction_id" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="transaction_date" compact="0" numFmtId="164" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="transaction_date_cleaned" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="merchant_name" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="merchant_name_cleaned" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="raw_amount" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="currency_value_in_USD" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="raw_amount_USD" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="currency" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="status" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="status_cleaned" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="risk_score" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="risk_score_cleaned" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="gateway_region" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="gateway_region_cleaned" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="descending">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea>
+          <references>
+            <reference field="4294967294">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField name="user_id" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="payment_method" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="high_value_flag" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="high_risk_flag" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields>
+    <field x="14"/>
+  </rowFields>
+  <colFields>
+    <field x="-2"/>
+  </colFields>
+  <dataFields>
+    <dataField name="SUM of raw_amount_USD" fld="7" baseField="0"/>
+    <dataField name="SUM of raw_amount" fld="5" baseField="0"/>
+  </dataFields>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTables 2" cacheId="0" dataCaption="" compact="0" compactData="0">
+  <location ref="E4:G9" firstHeaderRow="0" firstDataRow="2" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
+  <pivotFields>
+    <pivotField name="transaction_id" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="transaction_date" compact="0" numFmtId="164" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="transaction_date_cleaned" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="merchant_name" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="merchant_name_cleaned" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="descending">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea>
+          <references>
+            <reference field="4294967294">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField name="raw_amount" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="currency_value_in_USD" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="raw_amount_USD" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="currency" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="status" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="status_cleaned" axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="risk_score" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="risk_score_cleaned" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="gateway_region" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="gateway_region_cleaned" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="user_id" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="payment_method" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="high_value_flag" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="high_risk_flag" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields>
+    <field x="4"/>
+  </rowFields>
+  <colFields>
+    <field x="-2"/>
+  </colFields>
+  <pageFields>
+    <pageField fld="10"/>
+  </pageFields>
+  <dataFields>
+    <dataField name="SUM of raw_amount_USD" fld="7" baseField="0"/>
+    <dataField name="SUM of raw_amount" fld="5" baseField="0"/>
+  </dataFields>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -691,6 +1914,3129 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" ht="15.75" hidden="1" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="4">
+        <v>46082.0</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <f t="shared" ref="C2:C31" si="1">TEXT(if(or(B2="", B2="UNKNOWN", B2="ERROR"), "1900-01-01", B2), "YYYY_MM-DD")</f>
+        <v>2026_03-01</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1" t="str">
+        <f t="shared" ref="E2:E31" si="2">trim(if(OR(D2="", D2="ERROR", D2="UNKNOWN"), "INVALID_OR_MISSING", proper(D2)))</f>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F2" s="1">
+        <v>420000.0</v>
+      </c>
+      <c r="G2" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B2=exchange_rates!$A$2:$A$19, I2=exchange_rates!$B$2:$B$19)"),0.0119)</f>
+        <v>0.0119</v>
+      </c>
+      <c r="H2" s="1">
+        <f t="shared" ref="H2:H31" si="3">G2*F2</f>
+        <v>4998</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="1" t="str">
+        <f t="shared" ref="K2:K31" si="4">if(OR(J2="",J2 ="ERROR",J2 ="UNKNOWN"), "INVALID_OR_MISSING", proper(J2))</f>
+        <v>Captured</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="1">
+        <f t="shared" ref="M2:M31" si="5">if(OR(L2="",L2 ="ERROR",L2 ="UNKNOWN"), "INVALID_OR_MISSING", value(RIGHT(L2, 2)))</f>
+        <v>62</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E2=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="5">
+        <f t="shared" ref="R2:R31" si="6">if(OR(AND(O2="APAC", H2&gt;5000), AND(O2="EU", H2&gt;6000), AND(O2="US", H2&gt;7000)), 1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="S2" s="5">
+        <f t="shared" ref="S2:S31" si="7">if(OR(ISNUMBER(SEARCH("chargeback",K2)), AND(ISNUMBER(M2), M2 &gt;= 70)), 1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" hidden="1" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="4">
+        <v>46082.0</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-01</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F3" s="1">
+        <v>210000.0</v>
+      </c>
+      <c r="G3" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B3=exchange_rates!$A$2:$A$19, I3=exchange_rates!$B$2:$B$19)"),0.0119)</f>
+        <v>0.0119</v>
+      </c>
+      <c r="H3" s="1">
+        <f t="shared" si="3"/>
+        <v>2499</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L3" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="M3" s="1">
+        <f t="shared" si="5"/>
+        <v>55</v>
+      </c>
+      <c r="O3" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E3=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="4">
+        <v>46082.0</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-01</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F4" s="1">
+        <v>510000.0</v>
+      </c>
+      <c r="G4" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B4=exchange_rates!$A$2:$A$19, I4=exchange_rates!$B$2:$B$19)"),0.0119)</f>
+        <v>0.0119</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" si="3"/>
+        <v>6069</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L4" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="M4" s="1">
+        <f t="shared" si="5"/>
+        <v>71</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E4=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="4">
+        <v>46083.0</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-02</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F5" s="1">
+        <v>160000.0</v>
+      </c>
+      <c r="G5" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B5=exchange_rates!$A$2:$A$19, I5=exchange_rates!$B$2:$B$19)"),0.012)</f>
+        <v>0.012</v>
+      </c>
+      <c r="H5" s="1">
+        <f t="shared" si="3"/>
+        <v>1920</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Failed E05 Timeout</v>
+      </c>
+      <c r="L5" s="1">
+        <v>68.0</v>
+      </c>
+      <c r="M5" s="1">
+        <f t="shared" si="5"/>
+        <v>68</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E5=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R5" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" hidden="1" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="4">
+        <v>46083.0</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-02</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F6" s="1">
+        <v>390000.0</v>
+      </c>
+      <c r="G6" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B6=exchange_rates!$A$2:$A$19, I6=exchange_rates!$B$2:$B$19)"),0.012)</f>
+        <v>0.012</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="3"/>
+        <v>4680</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L6" s="1">
+        <v>58.0</v>
+      </c>
+      <c r="M6" s="1">
+        <f t="shared" si="5"/>
+        <v>58</v>
+      </c>
+      <c r="O6" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E6=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R6" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="4">
+        <v>46083.0</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-02</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F7" s="1">
+        <v>275000.0</v>
+      </c>
+      <c r="G7" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B7=exchange_rates!$A$2:$A$19, I7=exchange_rates!$B$2:$B$19)"),0.012)</f>
+        <v>0.012</v>
+      </c>
+      <c r="H7" s="1">
+        <f t="shared" si="3"/>
+        <v>3300</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M7" s="1">
+        <f t="shared" si="5"/>
+        <v>64</v>
+      </c>
+      <c r="O7" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E7=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R7" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" hidden="1" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="4">
+        <v>46083.0</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-02</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F8" s="1">
+        <v>450000.0</v>
+      </c>
+      <c r="G8" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B8=exchange_rates!$A$2:$A$19, I8=exchange_rates!$B$2:$B$19)"),0.012)</f>
+        <v>0.012</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="3"/>
+        <v>5400</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Chargeback</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="M8" s="1">
+        <f t="shared" si="5"/>
+        <v>83</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O8" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E8=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R8" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="S8" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="4">
+        <v>46084.0</v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-03</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F9" s="1">
+        <v>340000.0</v>
+      </c>
+      <c r="G9" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B9=exchange_rates!$A$2:$A$19, I9=exchange_rates!$B$2:$B$19)"),0.0121)</f>
+        <v>0.0121</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" si="3"/>
+        <v>4114</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L9" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="M9" s="1">
+        <f t="shared" si="5"/>
+        <v>59</v>
+      </c>
+      <c r="O9" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E9=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R9" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="4">
+        <v>46084.0</v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-03</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F10" s="1">
+        <v>125000.0</v>
+      </c>
+      <c r="G10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B10=exchange_rates!$A$2:$A$19, I10=exchange_rates!$B$2:$B$19)"),0.0121)</f>
+        <v>0.0121</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="3"/>
+        <v>1512.5</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L10" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="M10" s="1">
+        <f t="shared" si="5"/>
+        <v>46</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E10=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R10" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="4">
+        <v>46084.0</v>
+      </c>
+      <c r="C11" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-03</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F11" s="1">
+        <v>610000.0</v>
+      </c>
+      <c r="G11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B11=exchange_rates!$A$2:$A$19, I11=exchange_rates!$B$2:$B$19)"),0.0121)</f>
+        <v>0.0121</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" si="3"/>
+        <v>7381</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M11" s="1">
+        <f t="shared" si="5"/>
+        <v>77</v>
+      </c>
+      <c r="O11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E11=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R11" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="S11" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" hidden="1" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="4">
+        <v>46084.0</v>
+      </c>
+      <c r="C12" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-03</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F12" s="1">
+        <v>195000.0</v>
+      </c>
+      <c r="G12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B12=exchange_rates!$A$2:$A$19, I12=exchange_rates!$B$2:$B$19)"),0.0121)</f>
+        <v>0.0121</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="3"/>
+        <v>2359.5</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K12" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Failed E05 Timeout</v>
+      </c>
+      <c r="M12" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>INVALID_OR_MISSING</v>
+      </c>
+      <c r="O12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E12=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R12" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="4">
+        <v>46085.0</v>
+      </c>
+      <c r="C13" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-04</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F13" s="1">
+        <v>250000.0</v>
+      </c>
+      <c r="G13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B13=exchange_rates!$A$2:$A$19, I13=exchange_rates!$B$2:$B$19)"),0.012)</f>
+        <v>0.012</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" si="3"/>
+        <v>3000</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13" s="1">
+        <f t="shared" si="5"/>
+        <v>61</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E13=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R13" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S13" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" hidden="1" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="4">
+        <v>46085.0</v>
+      </c>
+      <c r="C14" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-04</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F14" s="1">
+        <v>310000.0</v>
+      </c>
+      <c r="G14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B14=exchange_rates!$A$2:$A$19, I14=exchange_rates!$B$2:$B$19)"),0.012)</f>
+        <v>0.012</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="3"/>
+        <v>3720</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="1">
+        <f t="shared" si="5"/>
+        <v>54</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E14=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R14" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="4">
+        <v>46085.0</v>
+      </c>
+      <c r="C15" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-04</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F15" s="1">
+        <v>470000.0</v>
+      </c>
+      <c r="G15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B15=exchange_rates!$A$2:$A$19, I15=exchange_rates!$B$2:$B$19)"),0.012)</f>
+        <v>0.012</v>
+      </c>
+      <c r="H15" s="1">
+        <f t="shared" si="3"/>
+        <v>5640</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="M15" s="1">
+        <f t="shared" si="5"/>
+        <v>73</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E15=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R15" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="S15" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" hidden="1" customHeight="1">
+      <c r="A16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="4">
+        <v>46085.0</v>
+      </c>
+      <c r="C16" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-04</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F16" s="1">
+        <v>130000.0</v>
+      </c>
+      <c r="G16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B16=exchange_rates!$A$2:$A$19, I16=exchange_rates!$B$2:$B$19)"),0.012)</f>
+        <v>0.012</v>
+      </c>
+      <c r="H16" s="1">
+        <f t="shared" si="3"/>
+        <v>1560</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="M16" s="1">
+        <f t="shared" si="5"/>
+        <v>52</v>
+      </c>
+      <c r="O16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E16=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R16" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="4">
+        <v>46086.0</v>
+      </c>
+      <c r="C17" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-05</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F17" s="1">
+        <v>220000.0</v>
+      </c>
+      <c r="G17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B17=exchange_rates!$A$2:$A$19, I17=exchange_rates!$B$2:$B$19)"),0.0118)</f>
+        <v>0.0118</v>
+      </c>
+      <c r="H17" s="1">
+        <f t="shared" si="3"/>
+        <v>2596</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K17" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Failed E05 Timeout</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="M17" s="1">
+        <f t="shared" si="5"/>
+        <v>69</v>
+      </c>
+      <c r="O17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E17=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R17" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="4">
+        <v>46086.0</v>
+      </c>
+      <c r="C18" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-05</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F18" s="1">
+        <v>180000.0</v>
+      </c>
+      <c r="G18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B18=exchange_rates!$A$2:$A$19, I18=exchange_rates!$B$2:$B$19)"),0.0118)</f>
+        <v>0.0118</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="3"/>
+        <v>2124</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K18" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Failed E05 Timeout</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M18" s="1">
+        <f t="shared" si="5"/>
+        <v>72</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E18=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R18" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="4">
+        <v>46086.0</v>
+      </c>
+      <c r="C19" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-05</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F19" s="1">
+        <v>145000.0</v>
+      </c>
+      <c r="G19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B19=exchange_rates!$A$2:$A$19, I19=exchange_rates!$B$2:$B$19)"),0.0118)</f>
+        <v>0.0118</v>
+      </c>
+      <c r="H19" s="1">
+        <f t="shared" si="3"/>
+        <v>1711</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K19" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Chargeback</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="M19" s="1">
+        <f t="shared" si="5"/>
+        <v>86</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E19=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R19" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" hidden="1" customHeight="1">
+      <c r="A20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="4">
+        <v>46086.0</v>
+      </c>
+      <c r="C20" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-05</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F20" s="1">
+        <v>260000.0</v>
+      </c>
+      <c r="G20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B20=exchange_rates!$A$2:$A$19, I20=exchange_rates!$B$2:$B$19)"),0.0118)</f>
+        <v>0.0118</v>
+      </c>
+      <c r="H20" s="1">
+        <f t="shared" si="3"/>
+        <v>3068</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K20" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Failed E05 Timeout</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M20" s="1">
+        <f t="shared" si="5"/>
+        <v>67</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E20=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R20" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" hidden="1" customHeight="1">
+      <c r="A21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="4">
+        <v>46086.0</v>
+      </c>
+      <c r="C21" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-05</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F21" s="1">
+        <v>520000.0</v>
+      </c>
+      <c r="G21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B21=exchange_rates!$A$2:$A$19, I21=exchange_rates!$B$2:$B$19)"),0.0118)</f>
+        <v>0.0118</v>
+      </c>
+      <c r="H21" s="1">
+        <f t="shared" si="3"/>
+        <v>6136</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L21" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="M21" s="1">
+        <f t="shared" si="5"/>
+        <v>75</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E21=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R21" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="S21" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="4">
+        <v>46087.0</v>
+      </c>
+      <c r="C22" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-06</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F22" s="1">
+        <v>330000.0</v>
+      </c>
+      <c r="G22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B22=exchange_rates!$A$2:$A$19, I22=exchange_rates!$B$2:$B$19)"),0.0119)</f>
+        <v>0.0119</v>
+      </c>
+      <c r="H22" s="1">
+        <f t="shared" si="3"/>
+        <v>3927</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="M22" s="1">
+        <f t="shared" si="5"/>
+        <v>63</v>
+      </c>
+      <c r="O22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E22=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R22" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" hidden="1" customHeight="1">
+      <c r="A23" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" s="4">
+        <v>46087.0</v>
+      </c>
+      <c r="C23" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-06</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F23" s="1">
+        <v>410000.0</v>
+      </c>
+      <c r="G23" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B23=exchange_rates!$A$2:$A$19, I23=exchange_rates!$B$2:$B$19)"),0.0119)</f>
+        <v>0.0119</v>
+      </c>
+      <c r="H23" s="1">
+        <f t="shared" si="3"/>
+        <v>4879</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L23" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="M23" s="1">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O23" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E23=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R23" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" hidden="1" customHeight="1">
+      <c r="A24" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="4">
+        <v>46082.0</v>
+      </c>
+      <c r="C24" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-01</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>City Pharma</v>
+      </c>
+      <c r="F24" s="1">
+        <v>5200.0</v>
+      </c>
+      <c r="G24" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B24=exchange_rates!$A$2:$A$19, I24=exchange_rates!$B$2:$B$19)"),1.08)</f>
+        <v>1.08</v>
+      </c>
+      <c r="H24" s="1">
+        <f t="shared" si="3"/>
+        <v>5616</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K24" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L24" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="M24" s="1">
+        <f t="shared" si="5"/>
+        <v>42</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="O24" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E24=merchant_master!$B$2:$B$6)"),"EU")</f>
+        <v>EU</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R24" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" s="4">
+        <v>46083.0</v>
+      </c>
+      <c r="C25" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-02</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Eco Home</v>
+      </c>
+      <c r="F25" s="1">
+        <v>6100.0</v>
+      </c>
+      <c r="G25" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B25=exchange_rates!$A$2:$A$19, I25=exchange_rates!$B$2:$B$19)"),1.09)</f>
+        <v>1.09</v>
+      </c>
+      <c r="H25" s="1">
+        <f t="shared" si="3"/>
+        <v>6649</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K25" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Chargeback</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M25" s="1">
+        <f t="shared" si="5"/>
+        <v>65</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="O25" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E25=merchant_master!$B$2:$B$6)"),"EU")</f>
+        <v>EU</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R25" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="S25" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" hidden="1" customHeight="1">
+      <c r="A26" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="4">
+        <v>46084.0</v>
+      </c>
+      <c r="C26" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-03</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>City Pharma</v>
+      </c>
+      <c r="F26" s="1">
+        <v>2800.0</v>
+      </c>
+      <c r="G26" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B26=exchange_rates!$A$2:$A$19, I26=exchange_rates!$B$2:$B$19)"),1.08)</f>
+        <v>1.08</v>
+      </c>
+      <c r="H26" s="1">
+        <f t="shared" si="3"/>
+        <v>3024</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L26" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="M26" s="1">
+        <f t="shared" si="5"/>
+        <v>38</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O26" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E26=merchant_master!$B$2:$B$6)"),"EU")</f>
+        <v>EU</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R26" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" s="4">
+        <v>46086.0</v>
+      </c>
+      <c r="C27" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-05</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Eco Home</v>
+      </c>
+      <c r="F27" s="1">
+        <v>3300.0</v>
+      </c>
+      <c r="G27" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B27=exchange_rates!$A$2:$A$19, I27=exchange_rates!$B$2:$B$19)"),1.09)</f>
+        <v>1.09</v>
+      </c>
+      <c r="H27" s="1">
+        <f t="shared" si="3"/>
+        <v>3597</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K27" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Failed E05 Timeout</v>
+      </c>
+      <c r="L27" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="M27" s="1">
+        <f t="shared" si="5"/>
+        <v>44</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="O27" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E27=merchant_master!$B$2:$B$6)"),"EU")</f>
+        <v>EU</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R27" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" hidden="1" customHeight="1">
+      <c r="A28" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" s="4">
+        <v>46082.0</v>
+      </c>
+      <c r="C28" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-01</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Delta Travels</v>
+      </c>
+      <c r="F28" s="1">
+        <v>7200.0</v>
+      </c>
+      <c r="G28" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B28=exchange_rates!$A$2:$A$19, I28=exchange_rates!$B$2:$B$19)"),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="H28" s="1">
+        <f t="shared" si="3"/>
+        <v>7200</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K28" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L28" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="M28" s="1">
+        <f t="shared" si="5"/>
+        <v>49</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="O28" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E28=merchant_master!$B$2:$B$6)"),"US")</f>
+        <v>US</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R28" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="S28" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" hidden="1" customHeight="1">
+      <c r="A29" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" s="4">
+        <v>46083.0</v>
+      </c>
+      <c r="C29" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-02</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Delta Travels</v>
+      </c>
+      <c r="F29" s="1">
+        <v>3100.0</v>
+      </c>
+      <c r="G29" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B29=exchange_rates!$A$2:$A$19, I29=exchange_rates!$B$2:$B$19)"),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="H29" s="1">
+        <f t="shared" si="3"/>
+        <v>3100</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K29" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="M29" s="1">
+        <f t="shared" si="5"/>
+        <v>41</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O29" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E29=merchant_master!$B$2:$B$6)"),"US")</f>
+        <v>US</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R29" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" hidden="1" customHeight="1">
+      <c r="A30" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" s="4">
+        <v>46085.0</v>
+      </c>
+      <c r="C30" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-04</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Delta Travels</v>
+      </c>
+      <c r="F30" s="1">
+        <v>2500.0</v>
+      </c>
+      <c r="G30" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B30=exchange_rates!$A$2:$A$19, I30=exchange_rates!$B$2:$B$19)"),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="H30" s="1">
+        <f t="shared" si="3"/>
+        <v>2500</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K30" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Chargeback</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="M30" s="1">
+        <f t="shared" si="5"/>
+        <v>58</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O30" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E30=merchant_master!$B$2:$B$6)"),"US")</f>
+        <v>US</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R30" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" hidden="1" customHeight="1">
+      <c r="A31" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="4">
+        <v>46087.0</v>
+      </c>
+      <c r="C31" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-06</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Delta Travels</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1800.0</v>
+      </c>
+      <c r="G31" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B31=exchange_rates!$A$2:$A$19, I31=exchange_rates!$B$2:$B$19)"),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="H31" s="1">
+        <f t="shared" si="3"/>
+        <v>1800</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K31" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Failed E05 Timeout</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="M31" s="1">
+        <f t="shared" si="5"/>
+        <v>47</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O31" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E31=merchant_master!$B$2:$B$6)"),"US")</f>
+        <v>US</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R31" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="R32" s="6">
+        <f t="shared" ref="R32:S32" si="8">sum(R2:R31)</f>
+        <v>7</v>
+      </c>
+      <c r="S32" s="6">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+  </sheetData>
+  <autoFilter ref="$A$1:$AG$32">
+    <filterColumn colId="4">
+      <filters blank="1">
+        <filter val="Beta Stores"/>
+        <filter val="Eco Home"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="20.63"/>
+    <col customWidth="1" min="3" max="3" width="16.13"/>
+    <col customWidth="1" min="6" max="6" width="20.63"/>
+    <col customWidth="1" min="7" max="7" width="17.75"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+  </sheetData>
+  <drawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="12.63"/>
+    <col customWidth="1" min="2" max="2" width="12.88"/>
+    <col customWidth="1" min="3" max="3" width="20.88"/>
+    <col customWidth="1" min="4" max="4" width="16.25"/>
+    <col customWidth="1" min="5" max="5" width="21.75"/>
+    <col customWidth="1" min="6" max="6" width="12.63"/>
+    <col customWidth="1" min="7" max="7" width="22.63"/>
+    <col customWidth="1" min="8" max="8" width="17.75"/>
+    <col customWidth="1" min="9" max="9" width="10.5"/>
+    <col customWidth="1" min="10" max="10" width="18.0"/>
+    <col customWidth="1" min="11" max="11" width="15.5"/>
+    <col customWidth="1" min="13" max="13" width="19.0"/>
+    <col customWidth="1" min="15" max="15" width="22.25"/>
+    <col customWidth="1" min="17" max="17" width="17.25"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6"/>
+      <c r="AD1" s="6"/>
+      <c r="AE1" s="6"/>
+    </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>19</v>
@@ -713,7 +5059,7 @@
         <v>420000.0</v>
       </c>
       <c r="G2" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I2=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4"&amp;"nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B2=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.0119)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B2=exchange_rates!$A$2:$A$19, I2=exchange_rates!$B$2:$B$19)"),0.0119)</f>
         <v>0.0119</v>
       </c>
       <c r="H2" s="1">
@@ -741,7 +5087,7 @@
         <v>24</v>
       </c>
       <c r="O2" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E2,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E2=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P2" s="1" t="s">
@@ -749,14 +5095,6 @@
       </c>
       <c r="Q2" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="R2" s="5">
-        <f t="shared" ref="R2:R31" si="6">if(OR(AND(O2="APAC", H2&gt;5000), AND(O2="EU", H2&gt;6000), AND(O2="US", H2&gt;7000)), 1, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="S2" s="5">
-        <f t="shared" ref="S2:S31" si="7">if(OR(ISNUMBER(SEARCH("chargeback",J2)), AND(ISNUMBER(M2), M2 &gt;= 70)), 1, 0)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -781,7 +5119,7 @@
         <v>210000.0</v>
       </c>
       <c r="G3" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I3=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4"&amp;"nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B3=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.0119)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B3=exchange_rates!$A$2:$A$19, I3=exchange_rates!$B$2:$B$19)"),0.0119)</f>
         <v>0.0119</v>
       </c>
       <c r="H3" s="1">
@@ -806,7 +5144,7 @@
         <v>55</v>
       </c>
       <c r="O3" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E3,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E3=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P3" s="1" t="s">
@@ -814,14 +5152,6 @@
       </c>
       <c r="Q3" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="R3" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S3" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -846,7 +5176,7 @@
         <v>510000.0</v>
       </c>
       <c r="G4" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I4=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4"&amp;"nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B4=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.0119)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B4=exchange_rates!$A$2:$A$19, I4=exchange_rates!$B$2:$B$19)"),0.0119)</f>
         <v>0.0119</v>
       </c>
       <c r="H4" s="1">
@@ -874,7 +5204,7 @@
         <v>24</v>
       </c>
       <c r="O4" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E4,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E4=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P4" s="1" t="s">
@@ -882,14 +5212,6 @@
       </c>
       <c r="Q4" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="R4" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="S4" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -914,7 +5236,7 @@
         <v>160000.0</v>
       </c>
       <c r="G5" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I5=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4"&amp;"nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B5=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.012)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B5=exchange_rates!$A$2:$A$19, I5=exchange_rates!$B$2:$B$19)"),0.012)</f>
         <v>0.012</v>
       </c>
       <c r="H5" s="1">
@@ -942,7 +5264,7 @@
         <v>40</v>
       </c>
       <c r="O5" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E5,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E5=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P5" s="1" t="s">
@@ -950,14 +5272,6 @@
       </c>
       <c r="Q5" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="R5" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S5" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -982,7 +5296,7 @@
         <v>390000.0</v>
       </c>
       <c r="G6" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I6=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4"&amp;"nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B6=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.012)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B6=exchange_rates!$A$2:$A$19, I6=exchange_rates!$B$2:$B$19)"),0.012)</f>
         <v>0.012</v>
       </c>
       <c r="H6" s="1">
@@ -1007,7 +5321,7 @@
         <v>58</v>
       </c>
       <c r="O6" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E6,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E6=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P6" s="1" t="s">
@@ -1015,14 +5329,6 @@
       </c>
       <c r="Q6" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="R6" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S6" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -1047,7 +5353,7 @@
         <v>275000.0</v>
       </c>
       <c r="G7" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I7=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4"&amp;"nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B7=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.012)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B7=exchange_rates!$A$2:$A$19, I7=exchange_rates!$B$2:$B$19)"),0.012)</f>
         <v>0.012</v>
       </c>
       <c r="H7" s="1">
@@ -1072,7 +5378,7 @@
         <v>64</v>
       </c>
       <c r="O7" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E7,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E7=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P7" s="1" t="s">
@@ -1080,14 +5386,6 @@
       </c>
       <c r="Q7" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="R7" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S7" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -1112,7 +5410,7 @@
         <v>450000.0</v>
       </c>
       <c r="G8" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I8=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4"&amp;"nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B8=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.012)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B8=exchange_rates!$A$2:$A$19, I8=exchange_rates!$B$2:$B$19)"),0.012)</f>
         <v>0.012</v>
       </c>
       <c r="H8" s="1">
@@ -1140,7 +5438,7 @@
         <v>24</v>
       </c>
       <c r="O8" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E8,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E8=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P8" s="1" t="s">
@@ -1148,14 +5446,6 @@
       </c>
       <c r="Q8" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="R8" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="S8" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -1180,7 +5470,7 @@
         <v>340000.0</v>
       </c>
       <c r="G9" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I9=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4"&amp;"nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B9=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.0121)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B9=exchange_rates!$A$2:$A$19, I9=exchange_rates!$B$2:$B$19)"),0.0121)</f>
         <v>0.0121</v>
       </c>
       <c r="H9" s="1">
@@ -1205,7 +5495,7 @@
         <v>59</v>
       </c>
       <c r="O9" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E9,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E9=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P9" s="1" t="s">
@@ -1213,14 +5503,6 @@
       </c>
       <c r="Q9" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="R9" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S9" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -1245,7 +5527,7 @@
         <v>125000.0</v>
       </c>
       <c r="G10" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I10=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B10=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.0121)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B10=exchange_rates!$A$2:$A$19, I10=exchange_rates!$B$2:$B$19)"),0.0121)</f>
         <v>0.0121</v>
       </c>
       <c r="H10" s="1">
@@ -1273,7 +5555,7 @@
         <v>24</v>
       </c>
       <c r="O10" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E10,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E10=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P10" s="1" t="s">
@@ -1281,14 +5563,6 @@
       </c>
       <c r="Q10" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="R10" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S10" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -1313,7 +5587,7 @@
         <v>610000.0</v>
       </c>
       <c r="G11" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I11=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B11=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.0121)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B11=exchange_rates!$A$2:$A$19, I11=exchange_rates!$B$2:$B$19)"),0.0121)</f>
         <v>0.0121</v>
       </c>
       <c r="H11" s="1">
@@ -1338,7 +5612,7 @@
         <v>77</v>
       </c>
       <c r="O11" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E11,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E11=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P11" s="1" t="s">
@@ -1346,14 +5620,6 @@
       </c>
       <c r="Q11" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="R11" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="S11" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
@@ -1378,7 +5644,7 @@
         <v>195000.0</v>
       </c>
       <c r="G12" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I12=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B12=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.0121)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B12=exchange_rates!$A$2:$A$19, I12=exchange_rates!$B$2:$B$19)"),0.0121)</f>
         <v>0.0121</v>
       </c>
       <c r="H12" s="1">
@@ -1400,7 +5666,7 @@
         <v>INVALID_OR_MISSING</v>
       </c>
       <c r="O12" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E12,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E12=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P12" s="1" t="s">
@@ -1408,14 +5674,6 @@
       </c>
       <c r="Q12" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="R12" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S12" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -1440,7 +5698,7 @@
         <v>250000.0</v>
       </c>
       <c r="G13" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I13=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B13=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.012)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B13=exchange_rates!$A$2:$A$19, I13=exchange_rates!$B$2:$B$19)"),0.012)</f>
         <v>0.012</v>
       </c>
       <c r="H13" s="1">
@@ -1468,7 +5726,7 @@
         <v>24</v>
       </c>
       <c r="O13" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E13,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E13=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P13" s="1" t="s">
@@ -1476,14 +5734,6 @@
       </c>
       <c r="Q13" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="R13" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S13" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
@@ -1508,7 +5758,7 @@
         <v>310000.0</v>
       </c>
       <c r="G14" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I14=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B14=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.012)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B14=exchange_rates!$A$2:$A$19, I14=exchange_rates!$B$2:$B$19)"),0.012)</f>
         <v>0.012</v>
       </c>
       <c r="H14" s="1">
@@ -1536,7 +5786,7 @@
         <v>24</v>
       </c>
       <c r="O14" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E14,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E14=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P14" s="1" t="s">
@@ -1544,14 +5794,6 @@
       </c>
       <c r="Q14" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="R14" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -1576,7 +5818,7 @@
         <v>470000.0</v>
       </c>
       <c r="G15" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I15=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B15=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.012)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B15=exchange_rates!$A$2:$A$19, I15=exchange_rates!$B$2:$B$19)"),0.012)</f>
         <v>0.012</v>
       </c>
       <c r="H15" s="1">
@@ -1604,7 +5846,7 @@
         <v>24</v>
       </c>
       <c r="O15" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E15,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E15=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P15" s="1" t="s">
@@ -1612,14 +5854,6 @@
       </c>
       <c r="Q15" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="R15" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="S15" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
@@ -1644,7 +5878,7 @@
         <v>130000.0</v>
       </c>
       <c r="G16" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I16=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B16=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.012)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B16=exchange_rates!$A$2:$A$19, I16=exchange_rates!$B$2:$B$19)"),0.012)</f>
         <v>0.012</v>
       </c>
       <c r="H16" s="1">
@@ -1669,7 +5903,7 @@
         <v>52</v>
       </c>
       <c r="O16" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E16,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E16=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P16" s="1" t="s">
@@ -1677,14 +5911,6 @@
       </c>
       <c r="Q16" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="R16" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S16" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
@@ -1709,7 +5935,7 @@
         <v>220000.0</v>
       </c>
       <c r="G17" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I17=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B17=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.0118)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B17=exchange_rates!$A$2:$A$19, I17=exchange_rates!$B$2:$B$19)"),0.0118)</f>
         <v>0.0118</v>
       </c>
       <c r="H17" s="1">
@@ -1734,7 +5960,7 @@
         <v>69</v>
       </c>
       <c r="O17" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E17,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E17=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P17" s="1" t="s">
@@ -1742,14 +5968,6 @@
       </c>
       <c r="Q17" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="R17" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S17" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
@@ -1774,7 +5992,7 @@
         <v>180000.0</v>
       </c>
       <c r="G18" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I18=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B18=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.0118)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B18=exchange_rates!$A$2:$A$19, I18=exchange_rates!$B$2:$B$19)"),0.0118)</f>
         <v>0.0118</v>
       </c>
       <c r="H18" s="1">
@@ -1802,7 +6020,7 @@
         <v>40</v>
       </c>
       <c r="O18" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E18,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E18=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P18" s="1" t="s">
@@ -1810,14 +6028,6 @@
       </c>
       <c r="Q18" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="R18" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S18" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
@@ -1842,7 +6052,7 @@
         <v>145000.0</v>
       </c>
       <c r="G19" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I19=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B19=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.0118)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B19=exchange_rates!$A$2:$A$19, I19=exchange_rates!$B$2:$B$19)"),0.0118)</f>
         <v>0.0118</v>
       </c>
       <c r="H19" s="1">
@@ -1870,7 +6080,7 @@
         <v>24</v>
       </c>
       <c r="O19" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E19,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E19=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P19" s="1" t="s">
@@ -1878,14 +6088,6 @@
       </c>
       <c r="Q19" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="R19" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S19" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1910,7 +6112,7 @@
         <v>260000.0</v>
       </c>
       <c r="G20" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I20=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B20=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.0118)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B20=exchange_rates!$A$2:$A$19, I20=exchange_rates!$B$2:$B$19)"),0.0118)</f>
         <v>0.0118</v>
       </c>
       <c r="H20" s="1">
@@ -1938,7 +6140,7 @@
         <v>40</v>
       </c>
       <c r="O20" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E20,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E20=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P20" s="1" t="s">
@@ -1946,14 +6148,6 @@
       </c>
       <c r="Q20" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="R20" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S20" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -1978,7 +6172,7 @@
         <v>520000.0</v>
       </c>
       <c r="G21" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I21=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B21=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.0118)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B21=exchange_rates!$A$2:$A$19, I21=exchange_rates!$B$2:$B$19)"),0.0118)</f>
         <v>0.0118</v>
       </c>
       <c r="H21" s="1">
@@ -2006,7 +6200,7 @@
         <v>24</v>
       </c>
       <c r="O21" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E21,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E21=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P21" s="1" t="s">
@@ -2014,14 +6208,6 @@
       </c>
       <c r="Q21" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="R21" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="S21" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -2046,7 +6232,7 @@
         <v>330000.0</v>
       </c>
       <c r="G22" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I22=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B22=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.0119)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B22=exchange_rates!$A$2:$A$19, I22=exchange_rates!$B$2:$B$19)"),0.0119)</f>
         <v>0.0119</v>
       </c>
       <c r="H22" s="1">
@@ -2071,7 +6257,7 @@
         <v>63</v>
       </c>
       <c r="O22" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E22,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E22=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P22" s="1" t="s">
@@ -2079,14 +6265,6 @@
       </c>
       <c r="Q22" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="R22" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S22" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -2111,7 +6289,7 @@
         <v>410000.0</v>
       </c>
       <c r="G23" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I23=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B23=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),0.0119)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B23=exchange_rates!$A$2:$A$19, I23=exchange_rates!$B$2:$B$19)"),0.0119)</f>
         <v>0.0119</v>
       </c>
       <c r="H23" s="1">
@@ -2139,7 +6317,7 @@
         <v>24</v>
       </c>
       <c r="O23" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E23,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"APAC")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E23=merchant_master!$B$2:$B$6)"),"APAC")</f>
         <v>APAC</v>
       </c>
       <c r="P23" s="1" t="s">
@@ -2147,14 +6325,6 @@
       </c>
       <c r="Q23" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="R23" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S23" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -2179,7 +6349,7 @@
         <v>5200.0</v>
       </c>
       <c r="G24" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I24=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B24=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),1.08)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B24=exchange_rates!$A$2:$A$19, I24=exchange_rates!$B$2:$B$19)"),1.08)</f>
         <v>1.08</v>
       </c>
       <c r="H24" s="1">
@@ -2207,7 +6377,7 @@
         <v>90</v>
       </c>
       <c r="O24" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E24,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"EU")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E24=merchant_master!$B$2:$B$6)"),"EU")</f>
         <v>EU</v>
       </c>
       <c r="P24" s="1" t="s">
@@ -2215,14 +6385,6 @@
       </c>
       <c r="Q24" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="R24" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S24" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -2247,7 +6409,7 @@
         <v>6100.0</v>
       </c>
       <c r="G25" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I25=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B25=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),1.09)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B25=exchange_rates!$A$2:$A$19, I25=exchange_rates!$B$2:$B$19)"),1.09)</f>
         <v>1.09</v>
       </c>
       <c r="H25" s="1">
@@ -2275,7 +6437,7 @@
         <v>90</v>
       </c>
       <c r="O25" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E25,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"EU")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E25=merchant_master!$B$2:$B$6)"),"EU")</f>
         <v>EU</v>
       </c>
       <c r="P25" s="1" t="s">
@@ -2283,14 +6445,6 @@
       </c>
       <c r="Q25" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="R25" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="S25" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -2315,7 +6469,7 @@
         <v>2800.0</v>
       </c>
       <c r="G26" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I26=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B26=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),1.08)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B26=exchange_rates!$A$2:$A$19, I26=exchange_rates!$B$2:$B$19)"),1.08)</f>
         <v>1.08</v>
       </c>
       <c r="H26" s="1">
@@ -2343,7 +6497,7 @@
         <v>95</v>
       </c>
       <c r="O26" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E26,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"EU")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E26=merchant_master!$B$2:$B$6)"),"EU")</f>
         <v>EU</v>
       </c>
       <c r="P26" s="1" t="s">
@@ -2351,14 +6505,6 @@
       </c>
       <c r="Q26" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="R26" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S26" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -2383,7 +6529,7 @@
         <v>3300.0</v>
       </c>
       <c r="G27" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I27=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B27=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),1.09)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B27=exchange_rates!$A$2:$A$19, I27=exchange_rates!$B$2:$B$19)"),1.09)</f>
         <v>1.09</v>
       </c>
       <c r="H27" s="1">
@@ -2411,7 +6557,7 @@
         <v>90</v>
       </c>
       <c r="O27" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E27,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"EU")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E27=merchant_master!$B$2:$B$6)"),"EU")</f>
         <v>EU</v>
       </c>
       <c r="P27" s="1" t="s">
@@ -2419,14 +6565,6 @@
       </c>
       <c r="Q27" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="R27" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S27" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -2451,7 +6589,7 @@
         <v>7200.0</v>
       </c>
       <c r="G28" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I28=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B28=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),1.0)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B28=exchange_rates!$A$2:$A$19, I28=exchange_rates!$B$2:$B$19)"),1.0)</f>
         <v>1</v>
       </c>
       <c r="H28" s="1">
@@ -2479,7 +6617,7 @@
         <v>100</v>
       </c>
       <c r="O28" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E28,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"US")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E28=merchant_master!$B$2:$B$6)"),"US")</f>
         <v>US</v>
       </c>
       <c r="P28" s="1" t="s">
@@ -2487,14 +6625,6 @@
       </c>
       <c r="Q28" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="R28" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="S28" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -2519,7 +6649,7 @@
         <v>3100.0</v>
       </c>
       <c r="G29" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I29=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B29=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),1.0)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B29=exchange_rates!$A$2:$A$19, I29=exchange_rates!$B$2:$B$19)"),1.0)</f>
         <v>1</v>
       </c>
       <c r="H29" s="1">
@@ -2547,7 +6677,7 @@
         <v>104</v>
       </c>
       <c r="O29" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E29,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"US")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E29=merchant_master!$B$2:$B$6)"),"US")</f>
         <v>US</v>
       </c>
       <c r="P29" s="1" t="s">
@@ -2555,14 +6685,6 @@
       </c>
       <c r="Q29" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="R29" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S29" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -2587,7 +6709,7 @@
         <v>2500.0</v>
       </c>
       <c r="G30" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I30=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B30=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),1.0)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B30=exchange_rates!$A$2:$A$19, I30=exchange_rates!$B$2:$B$19)"),1.0)</f>
         <v>1</v>
       </c>
       <c r="H30" s="1">
@@ -2615,7 +6737,7 @@
         <v>104</v>
       </c>
       <c r="O30" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E30,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"US")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E30=merchant_master!$B$2:$B$6)"),"US")</f>
         <v>US</v>
       </c>
       <c r="P30" s="1" t="s">
@@ -2623,14 +6745,6 @@
       </c>
       <c r="Q30" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="R30" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S30" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
@@ -2655,7 +6769,7 @@
         <v>1800.0</v>
       </c>
       <c r="G31" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!C2:C19""), I31=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB"&amp;"4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!B2:B19""), B31=IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1jI6xvE5DuO7D5FJQ-Zus-XTCMMS9FUB4nCuQTw61PD8/edit?gid=40537420#gid=40537420"",""exchange_rates!A2:A19""))"),1.0)</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B31=exchange_rates!$A$2:$A$19, I31=exchange_rates!$B$2:$B$19)"),1.0)</f>
         <v>1</v>
       </c>
       <c r="H31" s="1">
@@ -2683,7 +6797,7 @@
         <v>104</v>
       </c>
       <c r="O31" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("VLOOKUP(E31,IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1c8dmeo1Llg3EfYlgkbY12QiVWQkWDFa09vUraIt7_f8/edit?gid=60813055#gid=60813055"",""merchant_master!B2:E6""),4, TRUE)"),"US")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E31=merchant_master!$B$2:$B$6)"),"US")</f>
         <v>US</v>
       </c>
       <c r="P31" s="1" t="s">
@@ -2691,14 +6805,6 @@
       </c>
       <c r="Q31" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="R31" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S31" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -3671,7 +7777,4171 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$1:$AG$31"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="12.63"/>
+    <col customWidth="1" min="2" max="2" width="12.88"/>
+    <col customWidth="1" min="3" max="3" width="20.88"/>
+    <col customWidth="1" min="4" max="4" width="16.25"/>
+    <col customWidth="1" min="5" max="5" width="21.75"/>
+    <col customWidth="1" min="6" max="6" width="12.63"/>
+    <col customWidth="1" min="7" max="7" width="22.63"/>
+    <col customWidth="1" min="8" max="8" width="17.75"/>
+    <col customWidth="1" min="9" max="9" width="10.5"/>
+    <col customWidth="1" min="10" max="10" width="18.0"/>
+    <col customWidth="1" min="11" max="11" width="15.5"/>
+    <col customWidth="1" min="13" max="13" width="19.0"/>
+    <col customWidth="1" min="15" max="15" width="22.25"/>
+    <col customWidth="1" min="17" max="17" width="17.25"/>
+    <col customWidth="1" min="18" max="18" width="16.13"/>
+    <col customWidth="1" min="19" max="19" width="14.75"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6"/>
+      <c r="AD1" s="6"/>
+      <c r="AE1" s="6"/>
+      <c r="AF1" s="6"/>
+      <c r="AG1" s="6"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="4">
+        <v>46082.0</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <f t="shared" ref="C2:C31" si="1">TEXT(if(or(B2="", B2="UNKNOWN", B2="ERROR"), "1900-01-01", B2), "YYYY_MM-DD")</f>
+        <v>2026_03-01</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1" t="str">
+        <f t="shared" ref="E2:E31" si="2">trim(if(OR(D2="", D2="ERROR", D2="UNKNOWN"), "INVALID_OR_MISSING", proper(D2)))</f>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F2" s="1">
+        <v>420000.0</v>
+      </c>
+      <c r="G2" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B2=exchange_rates!$A$2:$A$19, I2=exchange_rates!$B$2:$B$19)"),0.0119)</f>
+        <v>0.0119</v>
+      </c>
+      <c r="H2" s="1">
+        <f t="shared" ref="H2:H31" si="3">G2*F2</f>
+        <v>4998</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="1" t="str">
+        <f t="shared" ref="K2:K31" si="4">if(OR(J2="",J2 ="ERROR",J2 ="UNKNOWN"), "INVALID_OR_MISSING", proper(J2))</f>
+        <v>Captured</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="1">
+        <f t="shared" ref="M2:M31" si="5">if(OR(L2="",L2 ="ERROR",L2 ="UNKNOWN"), "INVALID_OR_MISSING", value(RIGHT(L2, 2)))</f>
+        <v>62</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E2=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="5">
+        <f t="shared" ref="R2:R31" si="6">if(OR(AND(O2="APAC", H2&gt;5000), AND(O2="EU", H2&gt;6000), AND(O2="US", H2&gt;7000)), 1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="S2" s="5">
+        <f t="shared" ref="S2:S31" si="7">if(OR(ISNUMBER(SEARCH("chargeback",K2)), AND(ISNUMBER(M2), M2 &gt;= 70)), 1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="4">
+        <v>46082.0</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-01</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F3" s="1">
+        <v>210000.0</v>
+      </c>
+      <c r="G3" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B3=exchange_rates!$A$2:$A$19, I3=exchange_rates!$B$2:$B$19)"),0.0119)</f>
+        <v>0.0119</v>
+      </c>
+      <c r="H3" s="1">
+        <f t="shared" si="3"/>
+        <v>2499</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L3" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="M3" s="1">
+        <f t="shared" si="5"/>
+        <v>55</v>
+      </c>
+      <c r="O3" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E3=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="4">
+        <v>46082.0</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-01</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F4" s="1">
+        <v>510000.0</v>
+      </c>
+      <c r="G4" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B4=exchange_rates!$A$2:$A$19, I4=exchange_rates!$B$2:$B$19)"),0.0119)</f>
+        <v>0.0119</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" si="3"/>
+        <v>6069</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L4" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="M4" s="1">
+        <f t="shared" si="5"/>
+        <v>71</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E4=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="4">
+        <v>46083.0</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-02</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F5" s="1">
+        <v>160000.0</v>
+      </c>
+      <c r="G5" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B5=exchange_rates!$A$2:$A$19, I5=exchange_rates!$B$2:$B$19)"),0.012)</f>
+        <v>0.012</v>
+      </c>
+      <c r="H5" s="1">
+        <f t="shared" si="3"/>
+        <v>1920</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Failed E05 Timeout</v>
+      </c>
+      <c r="L5" s="1">
+        <v>68.0</v>
+      </c>
+      <c r="M5" s="1">
+        <f t="shared" si="5"/>
+        <v>68</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E5=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R5" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="4">
+        <v>46083.0</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-02</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F6" s="1">
+        <v>390000.0</v>
+      </c>
+      <c r="G6" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B6=exchange_rates!$A$2:$A$19, I6=exchange_rates!$B$2:$B$19)"),0.012)</f>
+        <v>0.012</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="3"/>
+        <v>4680</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L6" s="1">
+        <v>58.0</v>
+      </c>
+      <c r="M6" s="1">
+        <f t="shared" si="5"/>
+        <v>58</v>
+      </c>
+      <c r="O6" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E6=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R6" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="4">
+        <v>46083.0</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-02</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F7" s="1">
+        <v>275000.0</v>
+      </c>
+      <c r="G7" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B7=exchange_rates!$A$2:$A$19, I7=exchange_rates!$B$2:$B$19)"),0.012)</f>
+        <v>0.012</v>
+      </c>
+      <c r="H7" s="1">
+        <f t="shared" si="3"/>
+        <v>3300</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M7" s="1">
+        <f t="shared" si="5"/>
+        <v>64</v>
+      </c>
+      <c r="O7" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E7=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R7" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="4">
+        <v>46083.0</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-02</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F8" s="1">
+        <v>450000.0</v>
+      </c>
+      <c r="G8" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B8=exchange_rates!$A$2:$A$19, I8=exchange_rates!$B$2:$B$19)"),0.012)</f>
+        <v>0.012</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="3"/>
+        <v>5400</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Chargeback</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="M8" s="1">
+        <f t="shared" si="5"/>
+        <v>83</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O8" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E8=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R8" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="S8" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="4">
+        <v>46084.0</v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-03</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F9" s="1">
+        <v>340000.0</v>
+      </c>
+      <c r="G9" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B9=exchange_rates!$A$2:$A$19, I9=exchange_rates!$B$2:$B$19)"),0.0121)</f>
+        <v>0.0121</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" si="3"/>
+        <v>4114</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L9" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="M9" s="1">
+        <f t="shared" si="5"/>
+        <v>59</v>
+      </c>
+      <c r="O9" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E9=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R9" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="4">
+        <v>46084.0</v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-03</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F10" s="1">
+        <v>125000.0</v>
+      </c>
+      <c r="G10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B10=exchange_rates!$A$2:$A$19, I10=exchange_rates!$B$2:$B$19)"),0.0121)</f>
+        <v>0.0121</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="3"/>
+        <v>1512.5</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L10" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="M10" s="1">
+        <f t="shared" si="5"/>
+        <v>46</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E10=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R10" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="4">
+        <v>46084.0</v>
+      </c>
+      <c r="C11" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-03</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F11" s="1">
+        <v>610000.0</v>
+      </c>
+      <c r="G11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B11=exchange_rates!$A$2:$A$19, I11=exchange_rates!$B$2:$B$19)"),0.0121)</f>
+        <v>0.0121</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" si="3"/>
+        <v>7381</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M11" s="1">
+        <f t="shared" si="5"/>
+        <v>77</v>
+      </c>
+      <c r="O11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E11=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R11" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="S11" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="4">
+        <v>46084.0</v>
+      </c>
+      <c r="C12" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-03</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F12" s="1">
+        <v>195000.0</v>
+      </c>
+      <c r="G12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B12=exchange_rates!$A$2:$A$19, I12=exchange_rates!$B$2:$B$19)"),0.0121)</f>
+        <v>0.0121</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="3"/>
+        <v>2359.5</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K12" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Failed E05 Timeout</v>
+      </c>
+      <c r="M12" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>INVALID_OR_MISSING</v>
+      </c>
+      <c r="O12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E12=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R12" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="4">
+        <v>46085.0</v>
+      </c>
+      <c r="C13" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-04</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F13" s="1">
+        <v>250000.0</v>
+      </c>
+      <c r="G13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B13=exchange_rates!$A$2:$A$19, I13=exchange_rates!$B$2:$B$19)"),0.012)</f>
+        <v>0.012</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" si="3"/>
+        <v>3000</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13" s="1">
+        <f t="shared" si="5"/>
+        <v>61</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E13=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R13" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S13" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="4">
+        <v>46085.0</v>
+      </c>
+      <c r="C14" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-04</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F14" s="1">
+        <v>310000.0</v>
+      </c>
+      <c r="G14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B14=exchange_rates!$A$2:$A$19, I14=exchange_rates!$B$2:$B$19)"),0.012)</f>
+        <v>0.012</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="3"/>
+        <v>3720</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="1">
+        <f t="shared" si="5"/>
+        <v>54</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E14=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R14" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="4">
+        <v>46085.0</v>
+      </c>
+      <c r="C15" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-04</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F15" s="1">
+        <v>470000.0</v>
+      </c>
+      <c r="G15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B15=exchange_rates!$A$2:$A$19, I15=exchange_rates!$B$2:$B$19)"),0.012)</f>
+        <v>0.012</v>
+      </c>
+      <c r="H15" s="1">
+        <f t="shared" si="3"/>
+        <v>5640</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="M15" s="1">
+        <f t="shared" si="5"/>
+        <v>73</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E15=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R15" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="S15" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="4">
+        <v>46085.0</v>
+      </c>
+      <c r="C16" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-04</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F16" s="1">
+        <v>130000.0</v>
+      </c>
+      <c r="G16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B16=exchange_rates!$A$2:$A$19, I16=exchange_rates!$B$2:$B$19)"),0.012)</f>
+        <v>0.012</v>
+      </c>
+      <c r="H16" s="1">
+        <f t="shared" si="3"/>
+        <v>1560</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="M16" s="1">
+        <f t="shared" si="5"/>
+        <v>52</v>
+      </c>
+      <c r="O16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E16=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R16" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="4">
+        <v>46086.0</v>
+      </c>
+      <c r="C17" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-05</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F17" s="1">
+        <v>220000.0</v>
+      </c>
+      <c r="G17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B17=exchange_rates!$A$2:$A$19, I17=exchange_rates!$B$2:$B$19)"),0.0118)</f>
+        <v>0.0118</v>
+      </c>
+      <c r="H17" s="1">
+        <f t="shared" si="3"/>
+        <v>2596</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K17" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Failed E05 Timeout</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="M17" s="1">
+        <f t="shared" si="5"/>
+        <v>69</v>
+      </c>
+      <c r="O17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E17=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R17" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="4">
+        <v>46086.0</v>
+      </c>
+      <c r="C18" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-05</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F18" s="1">
+        <v>180000.0</v>
+      </c>
+      <c r="G18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B18=exchange_rates!$A$2:$A$19, I18=exchange_rates!$B$2:$B$19)"),0.0118)</f>
+        <v>0.0118</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="3"/>
+        <v>2124</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K18" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Failed E05 Timeout</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M18" s="1">
+        <f t="shared" si="5"/>
+        <v>72</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E18=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R18" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="4">
+        <v>46086.0</v>
+      </c>
+      <c r="C19" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-05</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F19" s="1">
+        <v>145000.0</v>
+      </c>
+      <c r="G19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B19=exchange_rates!$A$2:$A$19, I19=exchange_rates!$B$2:$B$19)"),0.0118)</f>
+        <v>0.0118</v>
+      </c>
+      <c r="H19" s="1">
+        <f t="shared" si="3"/>
+        <v>1711</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K19" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Chargeback</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="M19" s="1">
+        <f t="shared" si="5"/>
+        <v>86</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E19=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R19" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="4">
+        <v>46086.0</v>
+      </c>
+      <c r="C20" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-05</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F20" s="1">
+        <v>260000.0</v>
+      </c>
+      <c r="G20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B20=exchange_rates!$A$2:$A$19, I20=exchange_rates!$B$2:$B$19)"),0.0118)</f>
+        <v>0.0118</v>
+      </c>
+      <c r="H20" s="1">
+        <f t="shared" si="3"/>
+        <v>3068</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K20" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Failed E05 Timeout</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M20" s="1">
+        <f t="shared" si="5"/>
+        <v>67</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E20=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R20" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="4">
+        <v>46086.0</v>
+      </c>
+      <c r="C21" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-05</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F21" s="1">
+        <v>520000.0</v>
+      </c>
+      <c r="G21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B21=exchange_rates!$A$2:$A$19, I21=exchange_rates!$B$2:$B$19)"),0.0118)</f>
+        <v>0.0118</v>
+      </c>
+      <c r="H21" s="1">
+        <f t="shared" si="3"/>
+        <v>6136</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L21" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="M21" s="1">
+        <f t="shared" si="5"/>
+        <v>75</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E21=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R21" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="S21" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="4">
+        <v>46087.0</v>
+      </c>
+      <c r="C22" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-06</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Beta Stores</v>
+      </c>
+      <c r="F22" s="1">
+        <v>330000.0</v>
+      </c>
+      <c r="G22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B22=exchange_rates!$A$2:$A$19, I22=exchange_rates!$B$2:$B$19)"),0.0119)</f>
+        <v>0.0119</v>
+      </c>
+      <c r="H22" s="1">
+        <f t="shared" si="3"/>
+        <v>3927</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="M22" s="1">
+        <f t="shared" si="5"/>
+        <v>63</v>
+      </c>
+      <c r="O22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E22=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R22" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" s="4">
+        <v>46087.0</v>
+      </c>
+      <c r="C23" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-06</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpha Mart</v>
+      </c>
+      <c r="F23" s="1">
+        <v>410000.0</v>
+      </c>
+      <c r="G23" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B23=exchange_rates!$A$2:$A$19, I23=exchange_rates!$B$2:$B$19)"),0.0119)</f>
+        <v>0.0119</v>
+      </c>
+      <c r="H23" s="1">
+        <f t="shared" si="3"/>
+        <v>4879</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L23" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="M23" s="1">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O23" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E23=merchant_master!$B$2:$B$6)"),"APAC")</f>
+        <v>APAC</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R23" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="4">
+        <v>46082.0</v>
+      </c>
+      <c r="C24" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-01</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>City Pharma</v>
+      </c>
+      <c r="F24" s="1">
+        <v>5200.0</v>
+      </c>
+      <c r="G24" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B24=exchange_rates!$A$2:$A$19, I24=exchange_rates!$B$2:$B$19)"),1.08)</f>
+        <v>1.08</v>
+      </c>
+      <c r="H24" s="1">
+        <f t="shared" si="3"/>
+        <v>5616</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K24" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L24" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="M24" s="1">
+        <f t="shared" si="5"/>
+        <v>42</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="O24" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E24=merchant_master!$B$2:$B$6)"),"EU")</f>
+        <v>EU</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R24" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" s="4">
+        <v>46083.0</v>
+      </c>
+      <c r="C25" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-02</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Eco Home</v>
+      </c>
+      <c r="F25" s="1">
+        <v>6100.0</v>
+      </c>
+      <c r="G25" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B25=exchange_rates!$A$2:$A$19, I25=exchange_rates!$B$2:$B$19)"),1.09)</f>
+        <v>1.09</v>
+      </c>
+      <c r="H25" s="1">
+        <f t="shared" si="3"/>
+        <v>6649</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K25" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Chargeback</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M25" s="1">
+        <f t="shared" si="5"/>
+        <v>65</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="O25" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E25=merchant_master!$B$2:$B$6)"),"EU")</f>
+        <v>EU</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R25" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="S25" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="4">
+        <v>46084.0</v>
+      </c>
+      <c r="C26" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-03</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>City Pharma</v>
+      </c>
+      <c r="F26" s="1">
+        <v>2800.0</v>
+      </c>
+      <c r="G26" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B26=exchange_rates!$A$2:$A$19, I26=exchange_rates!$B$2:$B$19)"),1.08)</f>
+        <v>1.08</v>
+      </c>
+      <c r="H26" s="1">
+        <f t="shared" si="3"/>
+        <v>3024</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L26" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="M26" s="1">
+        <f t="shared" si="5"/>
+        <v>38</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O26" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E26=merchant_master!$B$2:$B$6)"),"EU")</f>
+        <v>EU</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R26" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" s="4">
+        <v>46086.0</v>
+      </c>
+      <c r="C27" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-05</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Eco Home</v>
+      </c>
+      <c r="F27" s="1">
+        <v>3300.0</v>
+      </c>
+      <c r="G27" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B27=exchange_rates!$A$2:$A$19, I27=exchange_rates!$B$2:$B$19)"),1.09)</f>
+        <v>1.09</v>
+      </c>
+      <c r="H27" s="1">
+        <f t="shared" si="3"/>
+        <v>3597</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K27" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Failed E05 Timeout</v>
+      </c>
+      <c r="L27" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="M27" s="1">
+        <f t="shared" si="5"/>
+        <v>44</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="O27" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E27=merchant_master!$B$2:$B$6)"),"EU")</f>
+        <v>EU</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R27" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" s="4">
+        <v>46082.0</v>
+      </c>
+      <c r="C28" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-01</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Delta Travels</v>
+      </c>
+      <c r="F28" s="1">
+        <v>7200.0</v>
+      </c>
+      <c r="G28" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B28=exchange_rates!$A$2:$A$19, I28=exchange_rates!$B$2:$B$19)"),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="H28" s="1">
+        <f t="shared" si="3"/>
+        <v>7200</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K28" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L28" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="M28" s="1">
+        <f t="shared" si="5"/>
+        <v>49</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="O28" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E28=merchant_master!$B$2:$B$6)"),"US")</f>
+        <v>US</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R28" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="S28" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" s="4">
+        <v>46083.0</v>
+      </c>
+      <c r="C29" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-02</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Delta Travels</v>
+      </c>
+      <c r="F29" s="1">
+        <v>3100.0</v>
+      </c>
+      <c r="G29" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B29=exchange_rates!$A$2:$A$19, I29=exchange_rates!$B$2:$B$19)"),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="H29" s="1">
+        <f t="shared" si="3"/>
+        <v>3100</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K29" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Captured</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="M29" s="1">
+        <f t="shared" si="5"/>
+        <v>41</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O29" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E29=merchant_master!$B$2:$B$6)"),"US")</f>
+        <v>US</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R29" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" s="4">
+        <v>46085.0</v>
+      </c>
+      <c r="C30" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-04</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Delta Travels</v>
+      </c>
+      <c r="F30" s="1">
+        <v>2500.0</v>
+      </c>
+      <c r="G30" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B30=exchange_rates!$A$2:$A$19, I30=exchange_rates!$B$2:$B$19)"),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="H30" s="1">
+        <f t="shared" si="3"/>
+        <v>2500</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K30" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Chargeback</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="M30" s="1">
+        <f t="shared" si="5"/>
+        <v>58</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O30" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E30=merchant_master!$B$2:$B$6)"),"US")</f>
+        <v>US</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R30" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="4">
+        <v>46087.0</v>
+      </c>
+      <c r="C31" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026_03-06</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>Delta Travels</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1800.0</v>
+      </c>
+      <c r="G31" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("filter(exchange_rates!$C$2:C$19,B31=exchange_rates!$A$2:$A$19, I31=exchange_rates!$B$2:$B$19)"),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="H31" s="1">
+        <f t="shared" si="3"/>
+        <v>1800</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K31" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>Failed E05 Timeout</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="M31" s="1">
+        <f t="shared" si="5"/>
+        <v>47</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O31" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("Filter(merchant_master!$E$2:$E$6,E31=merchant_master!$B$2:$B$6)"),"US")</f>
+        <v>US</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R31" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="10">
+        <v>46082.0</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1200.0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="10">
+        <v>46082.0</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="3">
+        <v>900.0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="10">
+        <v>46083.0</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="10">
+        <v>46084.0</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="3">
+        <v>7200.0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="10">
+        <v>46084.0</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="3">
+        <v>950.0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="10">
+        <v>46085.0</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3300.0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8" s="10">
+        <v>46085.0</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" s="3">
+        <v>600.0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="10">
+        <v>46086.0</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="3">
+        <v>4100.0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="10">
+        <v>46086.0</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1800.0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="10">
+        <v>46082.0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.0119</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10">
+        <v>46082.0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10">
+        <v>46082.0</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10">
+        <v>46083.0</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10">
+        <v>46083.0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10">
+        <v>46083.0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10">
+        <v>46084.0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.0121</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10">
+        <v>46084.0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10">
+        <v>46084.0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10">
+        <v>46085.0</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10">
+        <v>46085.0</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10">
+        <v>46085.0</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10">
+        <v>46086.0</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.0118</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10">
+        <v>46086.0</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10">
+        <v>46086.0</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10">
+        <v>46087.0</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.0119</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10">
+        <v>46087.0</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10">
+        <v>46087.0</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1" ht="13.5" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="10">
+        <v>46082.0</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1200.0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="10">
+        <v>46082.0</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="3">
+        <v>850.0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="10">
+        <v>46083.0</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="10">
+        <v>46083.0</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2100.0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="10">
+        <v>46084.0</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="3">
+        <v>7200.0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="10">
+        <v>46084.0</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" s="3">
+        <v>950.0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="10">
+        <v>46085.0</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3300.0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B9" s="10">
+        <v>46085.0</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" s="3">
+        <v>640.0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="10">
+        <v>46086.0</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" s="3">
+        <v>4100.0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="10">
+        <v>46086.0</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2500.0</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="10">
+        <v>46032.0</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" s="10">
+        <v>46040.0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="10">
+        <v>46044.0</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="10">
+        <v>46054.0</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="10">
+        <v>46057.0</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" s="10">
+        <v>46061.0</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="10">
+        <v>46065.0</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="10">
+        <v>46068.0</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="10">
+        <v>46073.0</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C11" s="10">
+        <v>46078.0</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/02_spreadsheet/spreadsheet_workbook.xlsx
+++ b/02_spreadsheet/spreadsheet_workbook.xlsx
@@ -1914,7 +1914,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" ht="15.75" hidden="1" customHeight="1">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="15.75" hidden="1" customHeight="1">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="15.75" hidden="1" customHeight="1">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>42</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="15.75" hidden="1" customHeight="1">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>48</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="15.75" hidden="1" customHeight="1">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>55</v>
       </c>
@@ -2579,7 +2579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" ht="15.75" hidden="1" customHeight="1">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>59</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="15.75" hidden="1" customHeight="1">
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>65</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" ht="15.75" hidden="1" customHeight="1">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>70</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="15.75" hidden="1" customHeight="1">
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>80</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="15.75" hidden="1" customHeight="1">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>82</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="15.75" hidden="1" customHeight="1">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>86</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="15.75" hidden="1" customHeight="1">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>87</v>
       </c>
@@ -3516,7 +3516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" ht="15.75" hidden="1" customHeight="1">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>94</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="15.75" hidden="1" customHeight="1">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>97</v>
       </c>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="15.75" hidden="1" customHeight="1">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>101</v>
       </c>
@@ -3788,7 +3788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="15.75" hidden="1" customHeight="1">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>105</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" ht="15.75" hidden="1" customHeight="1">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>108</v>
       </c>
@@ -4903,14 +4903,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$1:$AG$32">
-    <filterColumn colId="4">
-      <filters blank="1">
-        <filter val="Beta Stores"/>
-        <filter val="Eco Home"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="$A$1:$AG$32"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>

--- a/02_spreadsheet/spreadsheet_workbook.xlsx
+++ b/02_spreadsheet/spreadsheet_workbook.xlsx
@@ -713,12 +713,12 @@
     </cacheField>
     <cacheField name="transaction_date_cleaned" numFmtId="0">
       <sharedItems>
-        <s v="2026_03-01"/>
-        <s v="2026_03-02"/>
-        <s v="2026_03-03"/>
-        <s v="2026_03-04"/>
-        <s v="2026_03-05"/>
-        <s v="2026_03-06"/>
+        <s v="2026-03-01"/>
+        <s v="2026-03-02"/>
+        <s v="2026-03-03"/>
+        <s v="2026-03-04"/>
+        <s v="2026-03-05"/>
+        <s v="2026-03-06"/>
       </sharedItems>
     </cacheField>
     <cacheField name="merchant_name" numFmtId="0">
@@ -1922,8 +1922,8 @@
         <v>46082.0</v>
       </c>
       <c r="C2" s="1" t="str">
-        <f t="shared" ref="C2:C31" si="1">TEXT(if(or(B2="", B2="UNKNOWN", B2="ERROR"), "1900-01-01", B2), "YYYY_MM-DD")</f>
-        <v>2026_03-01</v>
+        <f t="shared" ref="C2:C31" si="1">TEXT(if(or(B2="", B2="UNKNOWN", B2="ERROR"), "1900-01-01", B2), "YYYY-MM-DD")</f>
+        <v>2026-03-01</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>20</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="C3" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>28</v>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="C4" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>33</v>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="C5" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-02</v>
+        <v>2026-03-02</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>38</v>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="C6" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-02</v>
+        <v>2026-03-02</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>43</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="C7" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-02</v>
+        <v>2026-03-02</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>38</v>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="C8" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-02</v>
+        <v>2026-03-02</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>49</v>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="C9" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-03</v>
+        <v>2026-03-03</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>33</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="C10" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-03</v>
+        <v>2026-03-03</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>43</v>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="C11" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-03</v>
+        <v>2026-03-03</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>57</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="C12" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-03</v>
+        <v>2026-03-03</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>49</v>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="C13" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-04</v>
+        <v>2026-03-04</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>38</v>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C14" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-04</v>
+        <v>2026-03-04</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>20</v>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="C15" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-04</v>
+        <v>2026-03-04</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>38</v>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C16" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-04</v>
+        <v>2026-03-04</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>43</v>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="C17" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>38</v>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="C18" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>38</v>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="C19" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>33</v>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="C20" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>49</v>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="C21" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>43</v>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="C22" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-06</v>
+        <v>2026-03-06</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>84</v>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="C23" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-06</v>
+        <v>2026-03-06</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>28</v>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="C24" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>88</v>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="C25" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-02</v>
+        <v>2026-03-02</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>92</v>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="C26" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-03</v>
+        <v>2026-03-03</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>88</v>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C27" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>92</v>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="C28" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>98</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C29" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-02</v>
+        <v>2026-03-02</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>102</v>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="C30" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-04</v>
+        <v>2026-03-04</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>106</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="C31" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>2026_03-06</v>
+        <v>2026-03-06</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>98</v>
